--- a/course-design-2/outputs/tables/ch8/40_stage26_1_sensitivity_comparison.xlsx
+++ b/course-design-2/outputs/tables/ch8/40_stage26_1_sensitivity_comparison.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_口径并列表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_统计范围并列表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_与Stage26复现对照" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_三种划分并列表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SafeF补充对照" sheetId="4" state="visible" r:id="rId4"/>

--- a/course-design-2/outputs/tables/ch8/40_stage26_1_sensitivity_comparison.xlsx
+++ b/course-design-2/outputs/tables/ch8/40_stage26_1_sensitivity_comparison.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Stage26 Candidate 口径</t>
+          <t>Stage26 Candidate 统计范围</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -930,8 +930,6 @@
           <t>同一协议：A+B+C+D+E、固定 model_splits 同一 Random Split、固定 LightGBM 与 Stage25 技能阈值 / 文本维度（100 / 16），只在 random train 上拟合估计器</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -998,8 +996,6 @@
           <t>同一协议：仅使用发布日期最早的约 70%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1029,8 +1025,6 @@
           <t>与 Stage25 正式主模型协议一致</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1060,8 +1054,6 @@
           <t>主实验为 A+B+C+D+E；本行仅作补充对照，不替代主结果；特征维度 358</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1091,8 +1083,6 @@
           <t>只读引用既有正式结果（30 号表 09）</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1122,8 +1112,6 @@
           <t>只读引用既有正式结果（31 号表 04）</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
